--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:17:49+00:00</t>
+    <t>2026-02-16T12:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T12:54:10+00:00</t>
+    <t>2026-02-17T15:13:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T15:13:06+00:00</t>
+    <t>2026-02-18T10:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T10:14:45+00:00</t>
+    <t>2026-02-24T10:54:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:54:30+00:00</t>
+    <t>2026-02-25T08:08:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-birth-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T08:08:12+00:00</t>
+    <t>2026-02-25T13:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
